--- a/АБК/Том СОТ АБК/Журнал входного контроля СОТ АБК.xlsx
+++ b/АБК/Том СОТ АБК/Журнал входного контроля СОТ АБК.xlsx
@@ -576,7 +576,7 @@
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Рабочая документация 16/1/26-СОТ-Р, лист 4; исполнительная документация 16/1/26-ИД-АБК, лист 6. Количество материалов — по АОСР № 1-СОТ-АБК, 2-СОТ-АБК; оборудование — по исполнительной документации.</t>
+          <t>Рабочая документация 16/1/26-СОТ-Р, лист 4; исполнительная документация 16/1/26-СОТ-ИД-АБК, лист 2. Спецификация 16/1/26-СОТ-ИД-АБК.СО. Количество материалов — по АОСР № 1-СОТ-АБК, 2-СОТ-АБК; оборудование — по исполнительной документации.</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 6</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 6</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 6</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 6</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="K28" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 6</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 6</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 6</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 6</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
